--- a/data/trans_orig/IQ19A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ19A-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.825598534006084</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.984357631880737</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.288919241312906</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.282874539202469</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>1.741653791915453</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.173290121359547</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.660445667579193</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1.868203175019916</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>1.780623069018232</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>2.07054006202017</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>1.467542694423708</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>1.573737737238818</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,46; 2,33</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,58; 2,88</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,14; 1,62</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 1,65</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1,42; 2,25</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 2,97</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,36; 2,14</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1,45; 2,51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 2,13</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1,73; 2,61</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,29; 1,7</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 1,98</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.462137909043453</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.581183575951601</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.13983305755398</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>1.098844014269253</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>1.41863029837939</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>1.722611247776876</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.355635167408028</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>1.448542929990011</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1.530640145460609</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>1.732090288578844</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1.28584092215967</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>1.310565263003383</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.325785485705568</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.880541343400757</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.617782291283945</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.645232409997577</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.251163844710943</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2.966920426916172</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>2.138408118273223</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>2.505044903646132</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2.128813260776615</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>2.605519275388958</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>1.70046375232184</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>1.984409978473536</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,94</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,93</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,55; 2,23</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,55; 2,17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,23; 1,69</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,28; 1,74</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,69; 2,25</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 1,92</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,62; 2,34</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 2,33</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1,68; 2,13</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 1,91</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 1,92</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,4; 1,88</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.830523816367564</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.801649533740266</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.423657179651004</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.465927795218344</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1.936040611498693</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.632281059053968</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1.931344702341065</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.77438246009013</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1.882063173547636</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1.713184482097191</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1.679497391561282</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1.587831895982588</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,72</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,9</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1.55044045743596</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1.547236975864174</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.232266139780111</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1.277522503643996</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.690416754796182</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1.436081270129414</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>1.620880667108912</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>1.437495241309898</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1.676782724965602</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>1.540032696660857</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>1.505848169576441</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>1.404635398464027</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1,38; 2,28</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 1,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 2,44</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,27; 1,99</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,7; 2,81</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 2,25</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,21; 1,78</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 2,02</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 2,3</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 1,98</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1,41; 1,96</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,38; 1,88</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.233648436402355</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.172141385714505</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.693353806399184</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.737899882162285</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>2.249172465055116</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>1.922623299899745</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>2.3405230993377</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>2.326991874341215</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>2.132825313875416</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>1.913947200138816</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>1.91919906806786</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>1.879612953677859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +923,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,66</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,64</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,96</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,75</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.721147163057742</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.596376038122624</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.812094853441088</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.543816407681756</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>2.113264813200521</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>1.828629604052752</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.422118610710893</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1.599132653985105</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1.900844362857732</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>1.709277644936203</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1.6217307649556</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1.570627729568021</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>1,44; 2,17</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,45; 2,28</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,18; 1,8</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 2,18</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,78; 2,99</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 2,13</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,54; 2,73</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 2,29</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1,71; 2,48</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 2,01</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1,45; 2,17</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 2,08</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1.383342300241885</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.350705593011277</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1.475676721213495</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.265414153808128</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.701819187218727</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>1.522477635816191</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>1.213119817947331</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>1.348645640187465</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>1.614492538154361</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>1.482622712131854</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>1.411555048970042</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>1.381028058017149</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.277958182088984</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.963708038902398</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.443443374979169</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.988990293785845</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.812093739489783</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2.247457839923102</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1.775852839880377</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2.018077452451716</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>2.297599335275937</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>1.975390237467784</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>1.962079742955029</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>1.877564280356756</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.751767378721802</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.744735839227495</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.410972387940909</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.656424521082494</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>2.17366531549801</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>1.635982708757891</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1.958743283295676</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>1.844585012725521</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>1.986221608861382</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1.686907234625509</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>1.709644771731085</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>1.752200382640528</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>1.435012754297392</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.454944369169277</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.183667728338669</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.367195169368245</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>1.779061391614569</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>1.372918276811041</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>1.537640886850689</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1.519435606581647</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>1.707863494658695</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>1.471422973135545</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>1.453069214799055</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>1.509825579174087</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.165171184895671</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.277874556253005</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.797044900544967</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.177370604113148</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>2.992103683182883</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>2.128320260908484</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>2.733709364131337</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>2.292184050169696</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>2.475662366077451</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>2.014357033206375</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>2.174118991676577</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>2.075483872876631</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>1,6; 2,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 2,03</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,36; 1,69</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 1,68</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,8; 2,26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,62; 1,99</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,61; 2,06</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1,59; 2,0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1,75; 2,05</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1,66; 1,94</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1,52; 1,79</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 1,76</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.786825818666424</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.782453159258854</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.48086844616021</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.502659336363387</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.993241561919901</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.777420584992033</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1.779456636127368</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>1.764156338362921</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1.892420671133467</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1.779921737372992</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>1.632278737270179</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1.624855584934637</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1.596937231107316</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.609879991487878</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.357537641162079</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1.367164256115675</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>1.801622482204842</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1.623542336790238</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>1.611469245960365</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>1.587362794801572</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>1.752395683607792</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>1.664851541796112</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1.519608054587339</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>1.505309389254132</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.001312892169774</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.030666812008528</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.686592356787395</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.68380003308149</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.263751846685783</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.990088529381051</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2.062265646559934</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>2.002802040345152</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>2.046604950324058</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>1.935848419508594</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>1.790761545174466</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1.761780115122304</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1329,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
